--- a/backend/data/templates/ClosingMessages_Template.xlsx
+++ b/backend/data/templates/ClosingMessages_Template.xlsx
@@ -4,6 +4,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="ClosingMessages" sheetId="1" r:id="rId1"/>
+    <sheet name="Legend" sheetId="2" r:id="rIdLegend1"/>
   </sheets>
 </workbook>
 </file>
@@ -35,7 +36,7 @@
   <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="11">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -43,16 +44,100 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5B4FC4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8E6F7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5B4FC4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8E6F7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -60,12 +145,76 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD0D0D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD0D0D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -121,10 +270,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
+        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
+        <a:font script="Hans" typeface="å®ä½"/>
+        <a:font script="Hant" typeface="æ°ç´°æé«"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -156,10 +305,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
+        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
+        <a:font script="Hans" typeface="å®ä½"/>
+        <a:font script="Hant" typeface="æ°ç´°æé«"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -395,9 +544,253 @@
 </a:theme>
 </file>
 
+<file path=xl/worksheets/legend.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FF5B4FC4"/>
+  </sheetPr>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="60" customWidth="1"/>
+    <col min="5" max="5" width="70" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Closing messages — how to fill in this template</t>
+        </is>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• This sheet is documentation only: it is ignored by the import. You can keep it in the file you upload.</t>
+        </is>
+      </c>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Do not rename, translate or reorder the column headers of the data sheet: they are matched exactly (case-sensitive).</t>
+        </is>
+      </c>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• One row per language. Re-uploading a language that already exists updates it; languages that are not in the file are left untouched.</t>
+        </is>
+      </c>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sheet "ClosingMessages"</t>
+        </is>
+      </c>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sheet</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Column</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Required</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What to enter</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="33" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ClosingMessages</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">language</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">English name of the language, exactly as in the platform language list (e.g. "English", "Italian"). Not case-sensitive.</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Native names ("Italiano") and language IDs are not accepted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="33" customHeight="1">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ClosingMessages</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">content</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HTML text. Recommended tags: &lt;p&gt;, &lt;h1&gt;/&lt;h2&gt;/&lt;h3&gt;, &lt;strong&gt;, &lt;em&gt;, &lt;u&gt;, &lt;a href="..."&gt;, &lt;ul&gt;/&lt;ol&gt; with &lt;li&gt;.</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shown once the patient has completed and submitted the questionnaire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="33" customHeight="1">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ClosingMessages</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">link_used_message</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HTML text.</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shown when a private link that has already completed the survey is opened again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="33" customHeight="1">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ClosingMessages</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">survey_closed_message</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HTML text.</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shown when the survey is not available (not started, ended, completed or disabled).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ClosingMessages</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">is_fallback</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"yes" = this language is shown when the patient's language is not available (it replaces the previous fallback). Blank = keep the current setting. Any other value (e.g. "no") = not the fallback.</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The first text uploaded for a survey is always the fallback. Do not set "no" on the current fallback without marking another language "yes": the survey would be left without one.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A7:E7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:E3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -413,9 +806,6 @@
         <v>survey_closed_message</v>
       </c>
       <c r="E1" t="str">
-        <v>resume_message</v>
-      </c>
-      <c r="F1" t="str">
         <v>is_fallback</v>
       </c>
     </row>
@@ -433,9 +823,6 @@
         <v>&lt;p&gt;This survey is now closed and is no longer available for completion. Thank you for your interest in this initiative.&lt;/p&gt;</v>
       </c>
       <c r="E2" t="str">
-        <v>&lt;p&gt;Welcome back! You can continue your questionnaire. Responses saved so far: {count}.&lt;/p&gt;</v>
-      </c>
-      <c r="F2" t="str">
         <v>yes</v>
       </c>
     </row>
@@ -453,15 +840,12 @@
         <v/>
       </c>
       <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
         <v>no</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
   </ignoredErrors>
 </worksheet>
 </file>